--- a/outputs/SAN/FC/SN3600B_FC/Config2_SN3600B_FC_Switch_EVALUATED_BOQ_Evaluated BOQ_Proposal.xlsx
+++ b/outputs/SAN/FC/SN3600B_FC/Config2_SN3600B_FC_Switch_EVALUATED_BOQ_Evaluated BOQ_Proposal.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Strategy Add-ons" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Base BOM'!A1:F6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Base BOM'!A1:F8</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -568,7 +568,7 @@
         <v>Base BOM Cost</v>
       </c>
       <c r="B7" s="6">
-        <v>82203</v>
+        <v>81496</v>
       </c>
     </row>
     <row r="8">
@@ -592,7 +592,7 @@
         <v>Total Estimated CapEx</v>
       </c>
       <c r="B10" s="7">
-        <v>62636</v>
+        <v>61929</v>
       </c>
     </row>
     <row r="12">
@@ -610,7 +610,7 @@
         <v>Validation</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>CLIC ACCEPTED — 2026-09-22T07:58:17.037Z</v>
+        <v>CLIC ACCEPTED — 2026-09-22T18:07:43.869Z</v>
       </c>
     </row>
     <row r="15">
@@ -630,7 +630,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -738,80 +738,128 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="str">
-        <v>HX2M2E</v>
+        <v>HA113A1</v>
       </c>
       <c r="B5" s="10">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="str">
-        <v>HPE 3 Year Tech Care Basic wCDMR SN3600B 24/8 8p 32Gb SW SFP Switch Service</v>
+        <v>HPE Installation Service</v>
       </c>
       <c r="D5" s="2" t="str">
         <v>Standard</v>
       </c>
       <c r="E5" s="11">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="F5" s="11">
         <f>B5*E5</f>
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="str">
-        <v>Standard Option</v>
+        <v>CONFIRMED ZERO-PRICE SERVICE PARENT</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="str">
-        <v>U5988E</v>
+        <v>HA113A1 5GA</v>
       </c>
       <c r="B6" s="10">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="str">
-        <v>HPE Installation Storage Switches Service</v>
+        <v>HPE LowEnd SAN/Edge Switch/HAFM Inst SVC</v>
       </c>
       <c r="D6" s="2" t="str">
         <v>Standard</v>
       </c>
       <c r="E6" s="11">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="F6" s="11">
         <f>B6*E6</f>
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="G6" s="2" t="str">
         <v>Standard Option</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="str">
+      <c r="A7" s="9" t="str">
+        <v>HU4B3A3</v>
+      </c>
+      <c r="B7" s="10">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <v>HPE 3Y Tech Care Basic with Defective Media Retention Service</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <v>Standard</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11">
+        <f>B7*E7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <v>CONFIRMED ZERO-PRICE SERVICE PARENT</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="str">
+        <v>HU4B3A3 ZTL</v>
+      </c>
+      <c r="B8" s="10">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>HPE SN3600B 24/8 8p 32G Swch Support</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <v>Standard</v>
+      </c>
+      <c r="E8" s="11">
+        <v>186</v>
+      </c>
+      <c r="F8" s="11">
+        <f>B8*E8</f>
+        <v>186</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>Standard Option</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="B7" s="10" t="str">
-        <v/>
-      </c>
-      <c r="C7" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D7" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E7" s="11" t="str">
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>SUM(F2:F6)</f>
-      </c>
-      <c r="G7" s="2" t="str">
+      <c r="B9" s="10" t="str">
+        <v/>
+      </c>
+      <c r="C9" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D9" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E9" s="11" t="str">
+        <v/>
+      </c>
+      <c r="F9" s="13">
+        <f>SUM(F2:F8)</f>
+      </c>
+      <c r="G9" s="2" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" selectLockedCells="1" selectUnlockedCells="1" formatCells="0" password="CC70"/>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F8"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
   </ignoredErrors>
 </worksheet>
 </file>
